--- a/artfynd/A 25521-2025 artfynd.xlsx
+++ b/artfynd/A 25521-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1653,6 +1653,714 @@
           <t>Ecogain</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126239487</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Östvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552043</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7037761</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126239384</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91254</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Östvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552102</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7037648</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126239495</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98247</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Östvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552039</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7037757</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126239366</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75060</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>308</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Östvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>552038</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7037548</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126239424</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Östvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>551728</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7038030</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126239443</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75052</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Östvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>552102</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7037673</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126239449</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75060</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>308</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Östvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>552102</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7037672</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25521-2025 artfynd.xlsx
+++ b/artfynd/A 25521-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>126239487</v>
       </c>
       <c r="B11" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>126239384</v>
       </c>
       <c r="B12" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>126239495</v>
       </c>
       <c r="B13" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126239366</v>
+        <v>126239424</v>
       </c>
       <c r="B14" t="n">
-        <v>75060</v>
+        <v>91238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552038</v>
+        <v>551728</v>
       </c>
       <c r="R14" t="n">
-        <v>7037548</v>
+        <v>7038030</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126239424</v>
+        <v>126239366</v>
       </c>
       <c r="B15" t="n">
-        <v>91236</v>
+        <v>75060</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551728</v>
+        <v>552038</v>
       </c>
       <c r="R15" t="n">
-        <v>7038030</v>
+        <v>7037548</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 25521-2025 artfynd.xlsx
+++ b/artfynd/A 25521-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>126239487</v>
       </c>
       <c r="B11" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>126239384</v>
       </c>
       <c r="B12" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>126239495</v>
       </c>
       <c r="B13" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126239424</v>
+        <v>126239366</v>
       </c>
       <c r="B14" t="n">
-        <v>91238</v>
+        <v>75064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551728</v>
+        <v>552038</v>
       </c>
       <c r="R14" t="n">
-        <v>7038030</v>
+        <v>7037548</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126239366</v>
+        <v>126239424</v>
       </c>
       <c r="B15" t="n">
-        <v>75060</v>
+        <v>91242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552038</v>
+        <v>551728</v>
       </c>
       <c r="R15" t="n">
-        <v>7037548</v>
+        <v>7038030</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2165,7 +2165,7 @@
         <v>126239443</v>
       </c>
       <c r="B16" t="n">
-        <v>75052</v>
+        <v>75056</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>126239449</v>
       </c>
       <c r="B17" t="n">
-        <v>75060</v>
+        <v>75064</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25521-2025 artfynd.xlsx
+++ b/artfynd/A 25521-2025 artfynd.xlsx
@@ -1861,7 +1861,7 @@
         <v>126239495</v>
       </c>
       <c r="B13" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 25521-2025 artfynd.xlsx
+++ b/artfynd/A 25521-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
         <v>126239487</v>
       </c>
       <c r="B11" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>126239384</v>
       </c>
       <c r="B12" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>126239495</v>
       </c>
       <c r="B13" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126239366</v>
+        <v>126239424</v>
       </c>
       <c r="B14" t="n">
-        <v>75064</v>
+        <v>91245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552038</v>
+        <v>551728</v>
       </c>
       <c r="R14" t="n">
-        <v>7037548</v>
+        <v>7038030</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126239424</v>
+        <v>126239366</v>
       </c>
       <c r="B15" t="n">
-        <v>91242</v>
+        <v>75067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551728</v>
+        <v>552038</v>
       </c>
       <c r="R15" t="n">
-        <v>7038030</v>
+        <v>7037548</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2165,7 +2165,7 @@
         <v>126239443</v>
       </c>
       <c r="B16" t="n">
-        <v>75056</v>
+        <v>75059</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>126239449</v>
       </c>
       <c r="B17" t="n">
-        <v>75064</v>
+        <v>75067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 25521-2025 artfynd.xlsx
+++ b/artfynd/A 25521-2025 artfynd.xlsx
@@ -1960,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126239424</v>
+        <v>126239366</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>75067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551728</v>
+        <v>552038</v>
       </c>
       <c r="R14" t="n">
-        <v>7038030</v>
+        <v>7037548</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126239366</v>
+        <v>126239424</v>
       </c>
       <c r="B15" t="n">
-        <v>75067</v>
+        <v>91245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552038</v>
+        <v>551728</v>
       </c>
       <c r="R15" t="n">
-        <v>7037548</v>
+        <v>7038030</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 25521-2025 artfynd.xlsx
+++ b/artfynd/A 25521-2025 artfynd.xlsx
@@ -2710,45 +2710,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133027511</v>
+        <v>133019580</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>91881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>230405</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551742</v>
+        <v>552028</v>
       </c>
       <c r="R21" t="n">
-        <v>7037946</v>
+        <v>7037496</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2817,10 +2817,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133027686</v>
+        <v>133022606</v>
       </c>
       <c r="B22" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2828,21 +2828,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551713</v>
+        <v>552064</v>
       </c>
       <c r="R22" t="n">
-        <v>7037997</v>
+        <v>7037661</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133022450</v>
+        <v>133027686</v>
       </c>
       <c r="B23" t="n">
-        <v>56522</v>
+        <v>92217</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2935,39 +2935,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206004</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552039</v>
+        <v>551713</v>
       </c>
       <c r="R23" t="n">
-        <v>7037638</v>
+        <v>7037997</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2999,7 +2994,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3009,7 +3004,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,45 +3138,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133019580</v>
+        <v>133018960</v>
       </c>
       <c r="B25" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552028</v>
+        <v>552057</v>
       </c>
       <c r="R25" t="n">
-        <v>7037496</v>
+        <v>7037527</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3223,7 +3223,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3250,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133022606</v>
+        <v>133023613</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3261,34 +3266,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552064</v>
+        <v>552120</v>
       </c>
       <c r="R26" t="n">
-        <v>7037661</v>
+        <v>7037650</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,7 +3330,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3330,7 +3340,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3357,10 +3367,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133018960</v>
+        <v>133022450</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>56522</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3368,42 +3378,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552057</v>
+        <v>552039</v>
       </c>
       <c r="R27" t="n">
-        <v>7037527</v>
+        <v>7037638</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3432,7 +3442,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3442,12 +3452,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,22 +3467,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133023613</v>
+        <v>133027511</v>
       </c>
       <c r="B28" t="n">
-        <v>57136</v>
+        <v>79334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,42 +3490,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>230405</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552120</v>
+        <v>551742</v>
       </c>
       <c r="R28" t="n">
-        <v>7037650</v>
+        <v>7037946</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3574,44 +3574,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133026638</v>
+        <v>133026664</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>92290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>551909</v>
+        <v>551892</v>
       </c>
       <c r="R29" t="n">
-        <v>7037936</v>
+        <v>7037942</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3681,19 +3681,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133025489</v>
+        <v>133026638</v>
       </c>
       <c r="B30" t="n">
         <v>79333</v>
@@ -3728,13 +3728,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>552004</v>
+        <v>551909</v>
       </c>
       <c r="R30" t="n">
-        <v>7037805</v>
+        <v>7037936</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3788,19 +3788,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133022364</v>
+        <v>133026237</v>
       </c>
       <c r="B31" t="n">
         <v>79333</v>
@@ -3835,13 +3835,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552045</v>
+        <v>551916</v>
       </c>
       <c r="R31" t="n">
-        <v>7037629</v>
+        <v>7037885</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3895,19 +3895,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133026237</v>
+        <v>133025489</v>
       </c>
       <c r="B32" t="n">
         <v>79333</v>
@@ -3942,13 +3942,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>551916</v>
+        <v>552004</v>
       </c>
       <c r="R32" t="n">
-        <v>7037885</v>
+        <v>7037805</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4002,19 +4002,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133026278</v>
+        <v>133022364</v>
       </c>
       <c r="B33" t="n">
         <v>79333</v>
@@ -4049,10 +4049,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>551921</v>
+        <v>552045</v>
       </c>
       <c r="R33" t="n">
-        <v>7037904</v>
+        <v>7037629</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4121,32 +4121,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133026664</v>
+        <v>133026278</v>
       </c>
       <c r="B34" t="n">
-        <v>92290</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>551892</v>
+        <v>551921</v>
       </c>
       <c r="R34" t="n">
-        <v>7037942</v>
+        <v>7037904</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133022667</v>
+        <v>133022506</v>
       </c>
       <c r="B35" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4239,21 +4239,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4263,13 +4263,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552069</v>
+        <v>552050</v>
       </c>
       <c r="R35" t="n">
-        <v>7037667</v>
+        <v>7037637</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4323,19 +4323,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133026585</v>
+        <v>133017033</v>
       </c>
       <c r="B36" t="n">
         <v>91918</v>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>551883</v>
+        <v>552005</v>
       </c>
       <c r="R36" t="n">
-        <v>7037940</v>
+        <v>7037676</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4442,10 +4442,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133017033</v>
+        <v>133022667</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,21 +4453,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552005</v>
+        <v>552069</v>
       </c>
       <c r="R37" t="n">
-        <v>7037676</v>
+        <v>7037667</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4549,32 +4549,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133022506</v>
+        <v>133027376</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>97243</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4584,13 +4584,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>552050</v>
+        <v>551758</v>
       </c>
       <c r="R38" t="n">
-        <v>7037637</v>
+        <v>7038023</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4644,44 +4644,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133027376</v>
+        <v>133026585</v>
       </c>
       <c r="B39" t="n">
-        <v>97243</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>551758</v>
+        <v>551883</v>
       </c>
       <c r="R39" t="n">
-        <v>7038023</v>
+        <v>7037940</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4880,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133025002</v>
+        <v>133028530</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,34 +4891,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>552071</v>
+        <v>551656</v>
       </c>
       <c r="R41" t="n">
-        <v>7037735</v>
+        <v>7038025</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4950,7 +4955,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4960,7 +4965,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4987,10 +4992,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133015718</v>
+        <v>133027021</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4998,34 +5003,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551979</v>
+        <v>551803</v>
       </c>
       <c r="R42" t="n">
-        <v>7037745</v>
+        <v>7037914</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5057,7 +5067,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5067,7 +5077,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5094,10 +5109,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133028530</v>
+        <v>133022367</v>
       </c>
       <c r="B43" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5105,16 +5120,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5134,13 +5149,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551656</v>
+        <v>552043</v>
       </c>
       <c r="R43" t="n">
-        <v>7038025</v>
+        <v>7037622</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5169,7 +5184,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5179,7 +5194,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5194,22 +5214,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133027021</v>
+        <v>133015718</v>
       </c>
       <c r="B44" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5217,39 +5237,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551803</v>
+        <v>551979</v>
       </c>
       <c r="R44" t="n">
-        <v>7037914</v>
+        <v>7037745</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5281,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5291,12 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5323,10 +5333,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133022367</v>
+        <v>133025002</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5334,42 +5344,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552043</v>
+        <v>552071</v>
       </c>
       <c r="R45" t="n">
-        <v>7037622</v>
+        <v>7037735</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5398,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5408,12 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5428,19 +5428,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133018625</v>
+        <v>133027884</v>
       </c>
       <c r="B46" t="n">
         <v>92217</v>
@@ -5468,20 +5468,29 @@
           <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>552060</v>
+        <v>551721</v>
       </c>
       <c r="R46" t="n">
-        <v>7037553</v>
+        <v>7037978</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5510,7 +5519,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5520,7 +5529,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5535,22 +5544,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133027884</v>
+        <v>133025648</v>
       </c>
       <c r="B47" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5558,43 +5567,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551721</v>
+        <v>551981</v>
       </c>
       <c r="R47" t="n">
-        <v>7037978</v>
+        <v>7037784</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5663,10 +5663,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133025648</v>
+        <v>133018625</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5674,37 +5674,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>551981</v>
+        <v>552060</v>
       </c>
       <c r="R48" t="n">
-        <v>7037784</v>
+        <v>7037553</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5758,12 +5758,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5994,10 +5994,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133019141</v>
+        <v>133022247</v>
       </c>
       <c r="B51" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6005,39 +6005,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>552062</v>
+        <v>552061</v>
       </c>
       <c r="R51" t="n">
-        <v>7037501</v>
+        <v>7037597</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6069,7 +6064,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6079,12 +6074,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6111,7 +6101,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133018677</v>
+        <v>133021235</v>
       </c>
       <c r="B52" t="n">
         <v>57958</v>
@@ -6151,10 +6141,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>552058</v>
+        <v>552097</v>
       </c>
       <c r="R52" t="n">
-        <v>7037536</v>
+        <v>7037521</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6186,7 +6176,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6196,7 +6186,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6228,10 +6218,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133022247</v>
+        <v>133019141</v>
       </c>
       <c r="B53" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6239,34 +6229,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>552061</v>
+        <v>552062</v>
       </c>
       <c r="R53" t="n">
-        <v>7037597</v>
+        <v>7037501</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6298,7 +6293,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6308,7 +6303,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6335,7 +6335,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133021235</v>
+        <v>133018677</v>
       </c>
       <c r="B54" t="n">
         <v>57958</v>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>552097</v>
+        <v>552058</v>
       </c>
       <c r="R54" t="n">
-        <v>7037521</v>
+        <v>7037536</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6564,10 +6564,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133023514</v>
+        <v>133027083</v>
       </c>
       <c r="B56" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6575,16 +6575,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6595,7 +6595,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6604,10 +6604,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>552097</v>
+        <v>551813</v>
       </c>
       <c r="R56" t="n">
-        <v>7037643</v>
+        <v>7037922</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6649,7 +6649,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6676,10 +6681,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133027083</v>
+        <v>133023514</v>
       </c>
       <c r="B57" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6687,16 +6692,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6707,7 +6712,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6716,10 +6721,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>551813</v>
+        <v>552097</v>
       </c>
       <c r="R57" t="n">
-        <v>7037922</v>
+        <v>7037643</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6751,7 +6756,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6761,12 +6766,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:56</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7358,10 +7358,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133017746</v>
+        <v>133025666</v>
       </c>
       <c r="B63" t="n">
-        <v>79333</v>
+        <v>91914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7369,34 +7369,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>552012</v>
+        <v>551986</v>
       </c>
       <c r="R63" t="n">
-        <v>7037589</v>
+        <v>7037773</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7465,7 +7465,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133027473</v>
+        <v>133025403</v>
       </c>
       <c r="B64" t="n">
         <v>79333</v>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>551721</v>
+        <v>552034</v>
       </c>
       <c r="R64" t="n">
-        <v>7038026</v>
+        <v>7037787</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7572,7 +7572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133025403</v>
+        <v>133016328</v>
       </c>
       <c r="B65" t="n">
         <v>79333</v>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>552034</v>
+        <v>552042</v>
       </c>
       <c r="R65" t="n">
-        <v>7037787</v>
+        <v>7037659</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7679,7 +7679,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133016328</v>
+        <v>133017746</v>
       </c>
       <c r="B66" t="n">
         <v>79333</v>
@@ -7710,14 +7710,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>552042</v>
+        <v>552012</v>
       </c>
       <c r="R66" t="n">
-        <v>7037659</v>
+        <v>7037589</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7786,10 +7786,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133025666</v>
+        <v>133027473</v>
       </c>
       <c r="B67" t="n">
-        <v>91914</v>
+        <v>79333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7797,21 +7797,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>551986</v>
+        <v>551721</v>
       </c>
       <c r="R67" t="n">
-        <v>7037773</v>
+        <v>7038026</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8127,10 +8127,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133016535</v>
+        <v>133016026</v>
       </c>
       <c r="B70" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8138,34 +8138,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>552017</v>
+        <v>552024</v>
       </c>
       <c r="R70" t="n">
-        <v>7037642</v>
+        <v>7037716</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8197,7 +8202,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8207,7 +8212,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8234,10 +8244,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133026891</v>
+        <v>133015837</v>
       </c>
       <c r="B71" t="n">
-        <v>79333</v>
+        <v>91914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8245,21 +8255,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8269,13 +8279,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>551825</v>
+        <v>551978</v>
       </c>
       <c r="R71" t="n">
-        <v>7037957</v>
+        <v>7037745</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8304,7 +8314,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8314,7 +8324,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8329,12 +8339,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8448,10 +8458,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133015837</v>
+        <v>133026958</v>
       </c>
       <c r="B73" t="n">
-        <v>91914</v>
+        <v>83181</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8459,21 +8469,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8483,13 +8493,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>551978</v>
+        <v>551810</v>
       </c>
       <c r="R73" t="n">
-        <v>7037745</v>
+        <v>7037968</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8518,7 +8528,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8528,7 +8538,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8543,22 +8553,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133026958</v>
+        <v>133016535</v>
       </c>
       <c r="B74" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8566,21 +8576,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8590,10 +8600,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>551810</v>
+        <v>552017</v>
       </c>
       <c r="R74" t="n">
-        <v>7037968</v>
+        <v>7037642</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8625,7 +8635,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8635,7 +8645,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8662,10 +8672,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133016026</v>
+        <v>133026891</v>
       </c>
       <c r="B75" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8673,39 +8683,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>552024</v>
+        <v>551825</v>
       </c>
       <c r="R75" t="n">
-        <v>7037716</v>
+        <v>7037957</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8737,7 +8742,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8747,12 +8752,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8886,7 +8886,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133016245</v>
+        <v>133021682</v>
       </c>
       <c r="B77" t="n">
         <v>57958</v>
@@ -8917,19 +8917,19 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>552066</v>
+        <v>552083</v>
       </c>
       <c r="R77" t="n">
-        <v>7037689</v>
+        <v>7037543</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -9003,7 +9003,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133017672</v>
+        <v>133016245</v>
       </c>
       <c r="B78" t="n">
         <v>57958</v>
@@ -9034,19 +9034,19 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>551991</v>
+        <v>552066</v>
       </c>
       <c r="R78" t="n">
-        <v>7037609</v>
+        <v>7037689</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -9120,7 +9120,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133021682</v>
+        <v>133026127</v>
       </c>
       <c r="B79" t="n">
         <v>57958</v>
@@ -9156,17 +9156,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>552083</v>
+        <v>551940</v>
       </c>
       <c r="R79" t="n">
-        <v>7037543</v>
+        <v>7037875</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9225,19 +9225,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133026127</v>
+        <v>133017672</v>
       </c>
       <c r="B80" t="n">
         <v>57958</v>
@@ -9273,17 +9273,17 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>551940</v>
+        <v>551991</v>
       </c>
       <c r="R80" t="n">
-        <v>7037875</v>
+        <v>7037609</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -9342,22 +9342,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133025358</v>
+        <v>133024612</v>
       </c>
       <c r="B81" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9365,42 +9365,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>552052</v>
+        <v>552097</v>
       </c>
       <c r="R81" t="n">
-        <v>7037780</v>
+        <v>7037685</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9429,7 +9424,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9439,12 +9434,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9459,19 +9449,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133026519</v>
+        <v>133025358</v>
       </c>
       <c r="B82" t="n">
         <v>57958</v>
@@ -9511,10 +9501,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>551914</v>
+        <v>552052</v>
       </c>
       <c r="R82" t="n">
-        <v>7037935</v>
+        <v>7037780</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9546,7 +9536,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9556,12 +9546,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack på gran, färska och äldre spår</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9588,7 +9578,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133015812</v>
+        <v>133026519</v>
       </c>
       <c r="B83" t="n">
         <v>57958</v>
@@ -9628,13 +9618,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>551983</v>
+        <v>551914</v>
       </c>
       <c r="R83" t="n">
-        <v>7037744</v>
+        <v>7037935</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9663,7 +9653,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9673,12 +9663,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på gran, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9693,19 +9683,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133025266</v>
+        <v>133017996</v>
       </c>
       <c r="B84" t="n">
         <v>57958</v>
@@ -9736,19 +9726,19 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>552072</v>
+        <v>552026</v>
       </c>
       <c r="R84" t="n">
-        <v>7037774</v>
+        <v>7037570</v>
       </c>
       <c r="S84" t="n">
         <v>20</v>
@@ -9780,7 +9770,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9790,12 +9780,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9822,10 +9812,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133024612</v>
+        <v>133015812</v>
       </c>
       <c r="B85" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9833,34 +9823,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>552097</v>
+        <v>551983</v>
       </c>
       <c r="R85" t="n">
-        <v>7037685</v>
+        <v>7037744</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9892,7 +9887,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9902,7 +9897,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9929,7 +9929,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133017996</v>
+        <v>133025266</v>
       </c>
       <c r="B86" t="n">
         <v>57958</v>
@@ -9960,19 +9960,19 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>552026</v>
+        <v>552072</v>
       </c>
       <c r="R86" t="n">
-        <v>7037570</v>
+        <v>7037774</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10046,10 +10046,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133020053</v>
+        <v>133025970</v>
       </c>
       <c r="B87" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10057,39 +10057,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>552014</v>
+        <v>551977</v>
       </c>
       <c r="R87" t="n">
-        <v>7037498</v>
+        <v>7037841</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10121,7 +10116,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10131,7 +10126,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10158,53 +10153,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133024456</v>
+        <v>133025202</v>
       </c>
       <c r="B88" t="n">
-        <v>57958</v>
+        <v>97243</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>552118</v>
+        <v>552070</v>
       </c>
       <c r="R88" t="n">
-        <v>7037678</v>
+        <v>7037765</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10233,7 +10223,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10243,12 +10233,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10263,19 +10248,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133027862</v>
+        <v>133017601</v>
       </c>
       <c r="B89" t="n">
         <v>57958</v>
@@ -10311,17 +10296,17 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>551707</v>
+        <v>551987</v>
       </c>
       <c r="R89" t="n">
-        <v>7038024</v>
+        <v>7037612</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10350,7 +10335,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10360,12 +10345,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10380,19 +10365,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133017601</v>
+        <v>133024456</v>
       </c>
       <c r="B90" t="n">
         <v>57958</v>
@@ -10423,22 +10408,22 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>551987</v>
+        <v>552118</v>
       </c>
       <c r="R90" t="n">
-        <v>7037612</v>
+        <v>7037678</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10467,7 +10452,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10477,7 +10462,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10497,22 +10482,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133025970</v>
+        <v>133027862</v>
       </c>
       <c r="B91" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10520,34 +10505,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>551977</v>
+        <v>551707</v>
       </c>
       <c r="R91" t="n">
-        <v>7037841</v>
+        <v>7038024</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10579,7 +10569,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10589,7 +10579,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10616,48 +10611,53 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133025202</v>
+        <v>133020053</v>
       </c>
       <c r="B92" t="n">
-        <v>97243</v>
+        <v>57955</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>552070</v>
+        <v>552014</v>
       </c>
       <c r="R92" t="n">
-        <v>7037765</v>
+        <v>7037498</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10711,22 +10711,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133027652</v>
+        <v>133016153</v>
       </c>
       <c r="B93" t="n">
-        <v>91918</v>
+        <v>57955</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10734,37 +10734,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>551711</v>
+        <v>552049</v>
       </c>
       <c r="R93" t="n">
-        <v>7037996</v>
+        <v>7037701</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10793,7 +10798,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10803,7 +10808,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10818,57 +10823,62 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133021299</v>
+        <v>133017323</v>
       </c>
       <c r="B94" t="n">
-        <v>97243</v>
+        <v>57958</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>552094</v>
+        <v>551983</v>
       </c>
       <c r="R94" t="n">
-        <v>7037523</v>
+        <v>7037658</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10900,7 +10910,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10910,7 +10920,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack, Färska och äldre spår på gran</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10937,10 +10952,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133016153</v>
+        <v>133022907</v>
       </c>
       <c r="B95" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10948,16 +10963,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10977,10 +10992,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>552049</v>
+        <v>552082</v>
       </c>
       <c r="R95" t="n">
-        <v>7037701</v>
+        <v>7037634</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -11012,7 +11027,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11022,7 +11037,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11049,7 +11069,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133022907</v>
+        <v>133027059</v>
       </c>
       <c r="B96" t="n">
         <v>57958</v>
@@ -11080,7 +11100,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11089,13 +11109,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>552082</v>
+        <v>551807</v>
       </c>
       <c r="R96" t="n">
-        <v>7037634</v>
+        <v>7037987</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11124,7 +11144,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11134,12 +11154,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11154,65 +11174,60 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133027059</v>
+        <v>133021299</v>
       </c>
       <c r="B97" t="n">
-        <v>57958</v>
+        <v>97243</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>551807</v>
+        <v>552094</v>
       </c>
       <c r="R97" t="n">
-        <v>7037987</v>
+        <v>7037523</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11241,7 +11256,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11251,12 +11266,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11271,22 +11281,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133017323</v>
+        <v>133027652</v>
       </c>
       <c r="B98" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11294,42 +11304,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>551983</v>
+        <v>551711</v>
       </c>
       <c r="R98" t="n">
-        <v>7037658</v>
+        <v>7037996</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11358,7 +11363,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11368,12 +11373,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, Färska och äldre spår på gran</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11388,22 +11388,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133018066</v>
+        <v>133016003</v>
       </c>
       <c r="B99" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11411,34 +11411,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>552023</v>
+        <v>552021</v>
       </c>
       <c r="R99" t="n">
-        <v>7037560</v>
+        <v>7037732</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11507,7 +11507,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133016003</v>
+        <v>133027333</v>
       </c>
       <c r="B100" t="n">
         <v>79333</v>
@@ -11542,10 +11542,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>552021</v>
+        <v>551760</v>
       </c>
       <c r="R100" t="n">
-        <v>7037732</v>
+        <v>7038027</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11614,7 +11614,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133016047</v>
+        <v>133019186</v>
       </c>
       <c r="B101" t="n">
         <v>79333</v>
@@ -11645,14 +11645,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>552035</v>
+        <v>552057</v>
       </c>
       <c r="R101" t="n">
-        <v>7037709</v>
+        <v>7037495</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11721,10 +11721,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133027333</v>
+        <v>133018066</v>
       </c>
       <c r="B102" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11732,34 +11732,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>551760</v>
+        <v>552023</v>
       </c>
       <c r="R102" t="n">
-        <v>7038027</v>
+        <v>7037560</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11828,7 +11828,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133019186</v>
+        <v>133016047</v>
       </c>
       <c r="B103" t="n">
         <v>79333</v>
@@ -11859,14 +11859,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>552057</v>
+        <v>552035</v>
       </c>
       <c r="R103" t="n">
-        <v>7037495</v>
+        <v>7037709</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12047,10 +12047,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133023664</v>
+        <v>133023354</v>
       </c>
       <c r="B105" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12058,39 +12058,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>552114</v>
+        <v>552115</v>
       </c>
       <c r="R105" t="n">
-        <v>7037653</v>
+        <v>7037637</v>
       </c>
       <c r="S105" t="n">
         <v>20</v>
@@ -12122,7 +12117,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12132,12 +12127,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12271,7 +12261,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133025281</v>
+        <v>133024875</v>
       </c>
       <c r="B107" t="n">
         <v>79333</v>
@@ -12306,13 +12296,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>552057</v>
+        <v>552088</v>
       </c>
       <c r="R107" t="n">
-        <v>7037781</v>
+        <v>7037696</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12341,7 +12331,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12351,7 +12341,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12366,19 +12356,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133023354</v>
+        <v>133025281</v>
       </c>
       <c r="B108" t="n">
         <v>79333</v>
@@ -12413,13 +12403,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>552115</v>
+        <v>552057</v>
       </c>
       <c r="R108" t="n">
-        <v>7037637</v>
+        <v>7037781</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12448,7 +12438,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12458,7 +12448,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12473,22 +12463,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133024875</v>
+        <v>133016445</v>
       </c>
       <c r="B109" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12496,34 +12486,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>552088</v>
+        <v>552020</v>
       </c>
       <c r="R109" t="n">
-        <v>7037696</v>
+        <v>7037641</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -12555,7 +12550,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12565,7 +12560,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12592,10 +12592,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133027032</v>
+        <v>133023664</v>
       </c>
       <c r="B110" t="n">
-        <v>57136</v>
+        <v>57958</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12603,16 +12603,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12623,7 +12623,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12632,13 +12632,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>551806</v>
+        <v>552114</v>
       </c>
       <c r="R110" t="n">
-        <v>7037991</v>
+        <v>7037653</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12677,7 +12677,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12692,22 +12697,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133016445</v>
+        <v>133027032</v>
       </c>
       <c r="B111" t="n">
-        <v>57958</v>
+        <v>57136</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12715,16 +12720,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12735,7 +12740,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -12744,13 +12749,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>552020</v>
+        <v>551806</v>
       </c>
       <c r="R111" t="n">
-        <v>7037641</v>
+        <v>7037991</v>
       </c>
       <c r="S111" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12779,7 +12784,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12789,12 +12794,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12809,12 +12809,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12937,7 +12937,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133016736</v>
+        <v>133017199</v>
       </c>
       <c r="B113" t="n">
         <v>83181</v>
@@ -12972,10 +12972,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>551998</v>
+        <v>551996</v>
       </c>
       <c r="R113" t="n">
-        <v>7037637</v>
+        <v>7037650</v>
       </c>
       <c r="S113" t="n">
         <v>20</v>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13151,32 +13151,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>133017199</v>
+        <v>133022073</v>
       </c>
       <c r="B115" t="n">
-        <v>83181</v>
+        <v>92641</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>551996</v>
+        <v>552082</v>
       </c>
       <c r="R115" t="n">
-        <v>7037650</v>
+        <v>7037603</v>
       </c>
       <c r="S115" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13246,44 +13246,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133022073</v>
+        <v>133016736</v>
       </c>
       <c r="B116" t="n">
-        <v>92641</v>
+        <v>83181</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13293,13 +13293,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>552082</v>
+        <v>551998</v>
       </c>
       <c r="R116" t="n">
-        <v>7037603</v>
+        <v>7037637</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13353,12 +13353,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13472,10 +13472,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133026771</v>
+        <v>133027635</v>
       </c>
       <c r="B118" t="n">
-        <v>79333</v>
+        <v>91914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13483,21 +13483,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>551871</v>
+        <v>551706</v>
       </c>
       <c r="R118" t="n">
-        <v>7037938</v>
+        <v>7038000</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13542,7 +13542,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13579,10 +13579,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133028459</v>
+        <v>133026771</v>
       </c>
       <c r="B119" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13590,39 +13590,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>551661</v>
+        <v>551871</v>
       </c>
       <c r="R119" t="n">
-        <v>7038023</v>
+        <v>7037938</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13654,7 +13649,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13664,12 +13659,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13696,10 +13686,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133027635</v>
+        <v>133028459</v>
       </c>
       <c r="B120" t="n">
-        <v>91914</v>
+        <v>57958</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13707,34 +13697,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>551706</v>
+        <v>551661</v>
       </c>
       <c r="R120" t="n">
-        <v>7038000</v>
+        <v>7038023</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13766,7 +13761,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13776,7 +13771,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD120" t="b">

--- a/artfynd/A 25521-2025 artfynd.xlsx
+++ b/artfynd/A 25521-2025 artfynd.xlsx
@@ -2710,45 +2710,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133019580</v>
+        <v>133018960</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552028</v>
+        <v>552057</v>
       </c>
       <c r="R21" t="n">
-        <v>7037496</v>
+        <v>7037527</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2780,7 +2785,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2790,7 +2795,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2817,10 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133022606</v>
+        <v>133027511</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2828,16 +2838,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2852,13 +2862,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552064</v>
+        <v>551742</v>
       </c>
       <c r="R22" t="n">
-        <v>7037661</v>
+        <v>7037946</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2887,7 +2897,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2897,7 +2907,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,22 +2922,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133027686</v>
+        <v>133022450</v>
       </c>
       <c r="B23" t="n">
-        <v>92217</v>
+        <v>56522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2935,34 +2945,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>206004</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551713</v>
+        <v>552039</v>
       </c>
       <c r="R23" t="n">
-        <v>7037997</v>
+        <v>7037638</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +3009,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3004,7 +3019,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3138,50 +3153,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133018960</v>
+        <v>133019580</v>
       </c>
       <c r="B25" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>552057</v>
+        <v>552028</v>
       </c>
       <c r="R25" t="n">
-        <v>7037527</v>
+        <v>7037496</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3213,7 +3223,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3223,12 +3233,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3255,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133023613</v>
+        <v>133022606</v>
       </c>
       <c r="B26" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3266,39 +3271,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552120</v>
+        <v>552064</v>
       </c>
       <c r="R26" t="n">
-        <v>7037650</v>
+        <v>7037661</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3367,10 +3367,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133022450</v>
+        <v>133027686</v>
       </c>
       <c r="B27" t="n">
-        <v>56522</v>
+        <v>92217</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,39 +3378,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>552039</v>
+        <v>551713</v>
       </c>
       <c r="R27" t="n">
-        <v>7037638</v>
+        <v>7037997</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,7 +3437,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3452,7 +3447,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,10 +3474,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133027511</v>
+        <v>133023613</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>57136</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3490,37 +3485,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230405</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>551742</v>
+        <v>552120</v>
       </c>
       <c r="R28" t="n">
-        <v>7037946</v>
+        <v>7037650</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3574,12 +3574,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133026237</v>
+        <v>133025489</v>
       </c>
       <c r="B31" t="n">
         <v>79333</v>
@@ -3835,13 +3835,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>551916</v>
+        <v>552004</v>
       </c>
       <c r="R31" t="n">
-        <v>7037885</v>
+        <v>7037805</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3895,19 +3895,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133025489</v>
+        <v>133026237</v>
       </c>
       <c r="B32" t="n">
         <v>79333</v>
@@ -3942,13 +3942,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>552004</v>
+        <v>551916</v>
       </c>
       <c r="R32" t="n">
-        <v>7037805</v>
+        <v>7037885</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4002,12 +4002,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133022506</v>
+        <v>133025924</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4239,37 +4239,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>552050</v>
+        <v>551975</v>
       </c>
       <c r="R35" t="n">
-        <v>7037637</v>
+        <v>7037830</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4298,7 +4303,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4308,7 +4313,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4323,22 +4333,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133017033</v>
+        <v>133022506</v>
       </c>
       <c r="B36" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4346,21 +4356,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4370,13 +4380,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>552005</v>
+        <v>552050</v>
       </c>
       <c r="R36" t="n">
-        <v>7037676</v>
+        <v>7037637</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4405,7 +4415,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4415,7 +4425,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4430,22 +4440,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133022667</v>
+        <v>133017033</v>
       </c>
       <c r="B37" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,21 +4463,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4477,10 +4487,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>552069</v>
+        <v>552005</v>
       </c>
       <c r="R37" t="n">
-        <v>7037667</v>
+        <v>7037676</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4512,7 +4522,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4522,7 +4532,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4549,32 +4559,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133027376</v>
+        <v>133022667</v>
       </c>
       <c r="B38" t="n">
-        <v>97243</v>
+        <v>83181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4584,10 +4594,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>551758</v>
+        <v>552069</v>
       </c>
       <c r="R38" t="n">
-        <v>7038023</v>
+        <v>7037667</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4619,7 +4629,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4629,7 +4639,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4656,32 +4666,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133026585</v>
+        <v>133027376</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>97243</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4691,10 +4701,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>551883</v>
+        <v>551758</v>
       </c>
       <c r="R39" t="n">
-        <v>7037940</v>
+        <v>7038023</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4726,7 +4736,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4736,7 +4746,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4763,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133025924</v>
+        <v>133026585</v>
       </c>
       <c r="B40" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4774,39 +4784,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>551975</v>
+        <v>551883</v>
       </c>
       <c r="R40" t="n">
-        <v>7037830</v>
+        <v>7037940</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4838,7 +4843,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4848,12 +4853,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4992,10 +4992,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133027021</v>
+        <v>133025002</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5003,42 +5003,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>551803</v>
+        <v>552071</v>
       </c>
       <c r="R42" t="n">
-        <v>7037914</v>
+        <v>7037735</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5067,7 +5062,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5077,12 +5072,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5097,22 +5087,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133022367</v>
+        <v>133015718</v>
       </c>
       <c r="B43" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5120,39 +5110,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>552043</v>
+        <v>551979</v>
       </c>
       <c r="R43" t="n">
-        <v>7037622</v>
+        <v>7037745</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5184,7 +5169,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5194,12 +5179,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5226,10 +5206,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133015718</v>
+        <v>133027021</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5237,34 +5217,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551979</v>
+        <v>551803</v>
       </c>
       <c r="R44" t="n">
-        <v>7037745</v>
+        <v>7037914</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5296,7 +5281,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5306,7 +5291,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,10 +5323,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133025002</v>
+        <v>133022367</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5344,37 +5334,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552071</v>
+        <v>552043</v>
       </c>
       <c r="R45" t="n">
-        <v>7037735</v>
+        <v>7037622</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5403,7 +5398,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5413,7 +5408,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5428,12 +5428,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6101,10 +6101,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133021235</v>
+        <v>133017895</v>
       </c>
       <c r="B52" t="n">
-        <v>57958</v>
+        <v>56522</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6112,27 +6112,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>552097</v>
+        <v>552040</v>
       </c>
       <c r="R52" t="n">
-        <v>7037521</v>
+        <v>7037573</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6186,12 +6186,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6218,7 +6213,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133019141</v>
+        <v>133021235</v>
       </c>
       <c r="B53" t="n">
         <v>57958</v>
@@ -6258,13 +6253,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>552062</v>
+        <v>552097</v>
       </c>
       <c r="R53" t="n">
-        <v>7037501</v>
+        <v>7037521</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6293,7 +6288,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6303,7 +6298,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6323,19 +6318,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133018677</v>
+        <v>133019141</v>
       </c>
       <c r="B54" t="n">
         <v>57958</v>
@@ -6375,13 +6370,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>552058</v>
+        <v>552062</v>
       </c>
       <c r="R54" t="n">
-        <v>7037536</v>
+        <v>7037501</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6410,7 +6405,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6420,7 +6415,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6440,22 +6435,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133017895</v>
+        <v>133018677</v>
       </c>
       <c r="B55" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6463,27 +6458,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6492,10 +6487,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>552040</v>
+        <v>552058</v>
       </c>
       <c r="R55" t="n">
-        <v>7037573</v>
+        <v>7037536</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6527,7 +6522,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6537,7 +6532,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6564,10 +6564,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133027083</v>
+        <v>133023514</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6575,16 +6575,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6595,7 +6595,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6604,10 +6604,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>551813</v>
+        <v>552097</v>
       </c>
       <c r="R56" t="n">
-        <v>7037922</v>
+        <v>7037643</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6649,12 +6649,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:56</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6681,10 +6676,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133023514</v>
+        <v>133027083</v>
       </c>
       <c r="B57" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6692,16 +6687,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6712,7 +6707,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6721,10 +6716,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>552097</v>
+        <v>551813</v>
       </c>
       <c r="R57" t="n">
-        <v>7037643</v>
+        <v>7037922</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6756,7 +6751,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6766,7 +6761,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6900,10 +6900,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133024844</v>
+        <v>133023893</v>
       </c>
       <c r="B59" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6911,16 +6911,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6931,7 +6931,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6940,13 +6940,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>552094</v>
+        <v>552119</v>
       </c>
       <c r="R59" t="n">
-        <v>7037684</v>
+        <v>7037634</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7000,22 +7000,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133023893</v>
+        <v>133028686</v>
       </c>
       <c r="B60" t="n">
-        <v>57136</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7023,16 +7023,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7043,7 +7043,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7052,10 +7052,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>552119</v>
+        <v>551645</v>
       </c>
       <c r="R60" t="n">
-        <v>7037634</v>
+        <v>7038009</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7097,7 +7097,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7124,7 +7129,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133028686</v>
+        <v>133017265</v>
       </c>
       <c r="B61" t="n">
         <v>57958</v>
@@ -7164,13 +7169,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>551645</v>
+        <v>551991</v>
       </c>
       <c r="R61" t="n">
-        <v>7038009</v>
+        <v>7037644</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7199,7 +7204,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7209,7 +7214,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7229,22 +7234,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133017265</v>
+        <v>133024844</v>
       </c>
       <c r="B62" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7252,16 +7257,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7281,10 +7286,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>551991</v>
+        <v>552094</v>
       </c>
       <c r="R62" t="n">
-        <v>7037644</v>
+        <v>7037684</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7316,7 +7321,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7326,12 +7331,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7358,10 +7358,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133025666</v>
+        <v>133017746</v>
       </c>
       <c r="B63" t="n">
-        <v>91914</v>
+        <v>79333</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7369,34 +7369,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>551986</v>
+        <v>552012</v>
       </c>
       <c r="R63" t="n">
-        <v>7037773</v>
+        <v>7037589</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7465,7 +7465,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133025403</v>
+        <v>133027473</v>
       </c>
       <c r="B64" t="n">
         <v>79333</v>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>552034</v>
+        <v>551721</v>
       </c>
       <c r="R64" t="n">
-        <v>7037787</v>
+        <v>7038026</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7572,7 +7572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133016328</v>
+        <v>133025403</v>
       </c>
       <c r="B65" t="n">
         <v>79333</v>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>552042</v>
+        <v>552034</v>
       </c>
       <c r="R65" t="n">
-        <v>7037659</v>
+        <v>7037787</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7679,7 +7679,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133017746</v>
+        <v>133016328</v>
       </c>
       <c r="B66" t="n">
         <v>79333</v>
@@ -7710,14 +7710,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>552012</v>
+        <v>552042</v>
       </c>
       <c r="R66" t="n">
-        <v>7037589</v>
+        <v>7037659</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7786,10 +7786,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133027473</v>
+        <v>133025666</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>91914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7797,21 +7797,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>551721</v>
+        <v>551986</v>
       </c>
       <c r="R67" t="n">
-        <v>7038026</v>
+        <v>7037773</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8127,10 +8127,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133016026</v>
+        <v>133015837</v>
       </c>
       <c r="B70" t="n">
-        <v>57958</v>
+        <v>91914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8138,42 +8138,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>552024</v>
+        <v>551978</v>
       </c>
       <c r="R70" t="n">
-        <v>7037716</v>
+        <v>7037745</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8202,7 +8197,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8212,12 +8207,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8232,19 +8222,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133015837</v>
+        <v>133025092</v>
       </c>
       <c r="B71" t="n">
         <v>91914</v>
@@ -8279,10 +8269,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>551978</v>
+        <v>552069</v>
       </c>
       <c r="R71" t="n">
-        <v>7037745</v>
+        <v>7037749</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8314,7 +8304,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8324,7 +8314,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8351,10 +8341,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133025092</v>
+        <v>133016535</v>
       </c>
       <c r="B72" t="n">
-        <v>91914</v>
+        <v>79333</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8362,21 +8352,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8386,13 +8376,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>552069</v>
+        <v>552017</v>
       </c>
       <c r="R72" t="n">
-        <v>7037749</v>
+        <v>7037642</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8421,7 +8411,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8431,7 +8421,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8446,12 +8436,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8565,7 +8555,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133016535</v>
+        <v>133026891</v>
       </c>
       <c r="B74" t="n">
         <v>79333</v>
@@ -8600,10 +8590,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>552017</v>
+        <v>551825</v>
       </c>
       <c r="R74" t="n">
-        <v>7037642</v>
+        <v>7037957</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8635,7 +8625,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8645,7 +8635,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8672,10 +8662,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133026891</v>
+        <v>133016026</v>
       </c>
       <c r="B75" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8683,34 +8673,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>551825</v>
+        <v>552024</v>
       </c>
       <c r="R75" t="n">
-        <v>7037957</v>
+        <v>7037716</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8742,7 +8737,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8752,7 +8747,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10046,10 +10046,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133025970</v>
+        <v>133020053</v>
       </c>
       <c r="B87" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10057,34 +10057,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>551977</v>
+        <v>552014</v>
       </c>
       <c r="R87" t="n">
-        <v>7037841</v>
+        <v>7037498</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10116,7 +10121,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10126,7 +10131,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10153,32 +10158,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133025202</v>
+        <v>133025970</v>
       </c>
       <c r="B88" t="n">
-        <v>97243</v>
+        <v>79333</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10188,13 +10193,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>552070</v>
+        <v>551977</v>
       </c>
       <c r="R88" t="n">
-        <v>7037765</v>
+        <v>7037841</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10223,7 +10228,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10233,7 +10238,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10248,62 +10253,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133017601</v>
+        <v>133025202</v>
       </c>
       <c r="B89" t="n">
-        <v>57958</v>
+        <v>97243</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>551987</v>
+        <v>552070</v>
       </c>
       <c r="R89" t="n">
-        <v>7037612</v>
+        <v>7037765</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10345,12 +10345,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10377,7 +10372,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133024456</v>
+        <v>133017601</v>
       </c>
       <c r="B90" t="n">
         <v>57958</v>
@@ -10408,22 +10403,22 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>552118</v>
+        <v>551987</v>
       </c>
       <c r="R90" t="n">
-        <v>7037678</v>
+        <v>7037612</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10452,7 +10447,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10462,7 +10457,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10482,19 +10477,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133027862</v>
+        <v>133024456</v>
       </c>
       <c r="B91" t="n">
         <v>57958</v>
@@ -10525,7 +10520,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10534,10 +10529,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>551707</v>
+        <v>552118</v>
       </c>
       <c r="R91" t="n">
-        <v>7038024</v>
+        <v>7037678</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10569,7 +10564,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10579,12 +10574,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10611,10 +10606,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133020053</v>
+        <v>133027862</v>
       </c>
       <c r="B92" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10622,16 +10617,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10647,14 +10642,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>552014</v>
+        <v>551707</v>
       </c>
       <c r="R92" t="n">
-        <v>7037498</v>
+        <v>7038024</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10686,7 +10681,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10696,7 +10691,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10835,10 +10835,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133017323</v>
+        <v>133027652</v>
       </c>
       <c r="B94" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10846,42 +10846,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>551983</v>
+        <v>551711</v>
       </c>
       <c r="R94" t="n">
-        <v>7037658</v>
+        <v>7037996</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10910,7 +10905,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10920,12 +10915,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack, Färska och äldre spår på gran</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10940,62 +10930,57 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133022907</v>
+        <v>133021299</v>
       </c>
       <c r="B95" t="n">
-        <v>57958</v>
+        <v>97243</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>552082</v>
+        <v>552094</v>
       </c>
       <c r="R95" t="n">
-        <v>7037634</v>
+        <v>7037523</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -11027,7 +11012,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11037,12 +11022,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11069,7 +11049,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133027059</v>
+        <v>133017323</v>
       </c>
       <c r="B96" t="n">
         <v>57958</v>
@@ -11100,7 +11080,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11109,13 +11089,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>551807</v>
+        <v>551983</v>
       </c>
       <c r="R96" t="n">
-        <v>7037987</v>
+        <v>7037658</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11144,7 +11124,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11154,12 +11134,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, Färska och äldre spår på gran</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11174,57 +11154,62 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133021299</v>
+        <v>133022907</v>
       </c>
       <c r="B97" t="n">
-        <v>97243</v>
+        <v>57958</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>552094</v>
+        <v>552082</v>
       </c>
       <c r="R97" t="n">
-        <v>7037523</v>
+        <v>7037634</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -11256,7 +11241,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11266,7 +11251,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11293,10 +11283,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133027652</v>
+        <v>133027059</v>
       </c>
       <c r="B98" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11304,34 +11294,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>551711</v>
+        <v>551807</v>
       </c>
       <c r="R98" t="n">
-        <v>7037996</v>
+        <v>7037987</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11363,7 +11358,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11373,7 +11368,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11400,10 +11400,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133016003</v>
+        <v>133026365</v>
       </c>
       <c r="B99" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11411,37 +11411,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>552021</v>
+        <v>551913</v>
       </c>
       <c r="R99" t="n">
-        <v>7037732</v>
+        <v>7037904</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11470,7 +11475,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11480,7 +11485,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11495,19 +11500,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133027333</v>
+        <v>133016003</v>
       </c>
       <c r="B100" t="n">
         <v>79333</v>
@@ -11542,10 +11547,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>551760</v>
+        <v>552021</v>
       </c>
       <c r="R100" t="n">
-        <v>7038027</v>
+        <v>7037732</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11577,7 +11582,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11587,7 +11592,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11614,7 +11619,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133019186</v>
+        <v>133016047</v>
       </c>
       <c r="B101" t="n">
         <v>79333</v>
@@ -11645,14 +11650,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>552057</v>
+        <v>552035</v>
       </c>
       <c r="R101" t="n">
-        <v>7037495</v>
+        <v>7037709</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11684,7 +11689,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11694,7 +11699,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11721,10 +11726,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133018066</v>
+        <v>133027333</v>
       </c>
       <c r="B102" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11732,34 +11737,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>552023</v>
+        <v>551760</v>
       </c>
       <c r="R102" t="n">
-        <v>7037560</v>
+        <v>7038027</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11791,7 +11796,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11801,7 +11806,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11828,7 +11833,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133016047</v>
+        <v>133019186</v>
       </c>
       <c r="B103" t="n">
         <v>79333</v>
@@ -11859,14 +11864,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>552035</v>
+        <v>552057</v>
       </c>
       <c r="R103" t="n">
-        <v>7037709</v>
+        <v>7037495</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11898,7 +11903,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11908,7 +11913,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11935,10 +11940,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133026365</v>
+        <v>133018066</v>
       </c>
       <c r="B104" t="n">
-        <v>57955</v>
+        <v>91918</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11946,42 +11951,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>551913</v>
+        <v>552023</v>
       </c>
       <c r="R104" t="n">
-        <v>7037904</v>
+        <v>7037560</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12035,22 +12035,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133023354</v>
+        <v>133027032</v>
       </c>
       <c r="B105" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12058,37 +12058,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>552115</v>
+        <v>551806</v>
       </c>
       <c r="R105" t="n">
-        <v>7037637</v>
+        <v>7037991</v>
       </c>
       <c r="S105" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12117,7 +12122,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12127,7 +12132,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12142,22 +12147,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133025768</v>
+        <v>133016445</v>
       </c>
       <c r="B106" t="n">
-        <v>83181</v>
+        <v>57958</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12165,37 +12170,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>551962</v>
+        <v>552020</v>
       </c>
       <c r="R106" t="n">
-        <v>7037809</v>
+        <v>7037641</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12224,7 +12234,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12234,7 +12244,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12249,22 +12264,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133024875</v>
+        <v>133023664</v>
       </c>
       <c r="B107" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12272,34 +12287,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>552088</v>
+        <v>552114</v>
       </c>
       <c r="R107" t="n">
-        <v>7037696</v>
+        <v>7037653</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -12331,7 +12351,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12341,7 +12361,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12475,10 +12500,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133016445</v>
+        <v>133023354</v>
       </c>
       <c r="B109" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12486,39 +12511,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>552020</v>
+        <v>552115</v>
       </c>
       <c r="R109" t="n">
-        <v>7037641</v>
+        <v>7037637</v>
       </c>
       <c r="S109" t="n">
         <v>20</v>
@@ -12550,7 +12570,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12560,12 +12580,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12592,10 +12607,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133023664</v>
+        <v>133025768</v>
       </c>
       <c r="B110" t="n">
-        <v>57958</v>
+        <v>83181</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12603,42 +12618,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>552114</v>
+        <v>551962</v>
       </c>
       <c r="R110" t="n">
-        <v>7037653</v>
+        <v>7037809</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12667,7 +12677,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12677,12 +12687,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12697,22 +12702,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133027032</v>
+        <v>133024875</v>
       </c>
       <c r="B111" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12720,42 +12725,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>551806</v>
+        <v>552088</v>
       </c>
       <c r="R111" t="n">
-        <v>7037991</v>
+        <v>7037696</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12809,12 +12809,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>

--- a/artfynd/A 25521-2025 artfynd.xlsx
+++ b/artfynd/A 25521-2025 artfynd.xlsx
@@ -2364,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133024819</v>
+        <v>133024838</v>
       </c>
       <c r="B18" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2375,16 +2375,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2395,7 +2395,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2404,13 +2404,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552093</v>
+        <v>552081</v>
       </c>
       <c r="R18" t="n">
-        <v>7037682</v>
+        <v>7037695</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2449,12 +2449,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,19 +2464,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133021811</v>
+        <v>133024819</v>
       </c>
       <c r="B19" t="n">
         <v>57958</v>
@@ -2512,19 +2507,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552087</v>
+        <v>552093</v>
       </c>
       <c r="R19" t="n">
-        <v>7037572</v>
+        <v>7037682</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,7 +2551,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2566,7 +2561,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2598,10 +2593,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133024838</v>
+        <v>133021811</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,16 +2604,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2634,17 +2629,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552081</v>
+        <v>552087</v>
       </c>
       <c r="R20" t="n">
-        <v>7037695</v>
+        <v>7037572</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2673,7 +2668,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2683,7 +2678,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,22 +2698,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133018960</v>
+        <v>133019872</v>
       </c>
       <c r="B21" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,42 +2721,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552057</v>
+        <v>552009</v>
       </c>
       <c r="R21" t="n">
-        <v>7037527</v>
+        <v>7037493</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2785,7 +2780,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2795,12 +2790,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,22 +2805,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133027511</v>
+        <v>133022606</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2838,16 +2828,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2862,13 +2852,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551742</v>
+        <v>552064</v>
       </c>
       <c r="R22" t="n">
-        <v>7037946</v>
+        <v>7037661</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2897,7 +2887,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2907,7 +2897,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133022450</v>
+        <v>133023613</v>
       </c>
       <c r="B23" t="n">
-        <v>56522</v>
+        <v>57136</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2935,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206004</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2974,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>552039</v>
+        <v>552120</v>
       </c>
       <c r="R23" t="n">
-        <v>7037638</v>
+        <v>7037650</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,7 +2999,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3019,7 +3009,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3046,10 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133019872</v>
+        <v>133022450</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>56522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,34 +3047,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>552009</v>
+        <v>552039</v>
       </c>
       <c r="R24" t="n">
-        <v>7037493</v>
+        <v>7037638</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,7 +3111,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3126,7 +3121,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3255,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133022606</v>
+        <v>133027686</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,21 +3266,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3295,10 +3290,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>552064</v>
+        <v>551713</v>
       </c>
       <c r="R26" t="n">
-        <v>7037661</v>
+        <v>7037997</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,7 +3325,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3340,7 +3335,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3367,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133027686</v>
+        <v>133018960</v>
       </c>
       <c r="B27" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,37 +3373,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>551713</v>
+        <v>552057</v>
       </c>
       <c r="R27" t="n">
-        <v>7037997</v>
+        <v>7037527</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3447,7 +3447,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3462,22 +3467,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133023613</v>
+        <v>133027511</v>
       </c>
       <c r="B28" t="n">
-        <v>57136</v>
+        <v>79334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,42 +3490,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>230405</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>552120</v>
+        <v>551742</v>
       </c>
       <c r="R28" t="n">
-        <v>7037650</v>
+        <v>7037946</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3574,44 +3574,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133026664</v>
+        <v>133026638</v>
       </c>
       <c r="B29" t="n">
-        <v>92290</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3621,13 +3621,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>551892</v>
+        <v>551909</v>
       </c>
       <c r="R29" t="n">
-        <v>7037942</v>
+        <v>7037936</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3681,19 +3681,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133026638</v>
+        <v>133025489</v>
       </c>
       <c r="B30" t="n">
         <v>79333</v>
@@ -3728,13 +3728,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>551909</v>
+        <v>552004</v>
       </c>
       <c r="R30" t="n">
-        <v>7037936</v>
+        <v>7037805</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3788,19 +3788,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133025489</v>
+        <v>133026237</v>
       </c>
       <c r="B31" t="n">
         <v>79333</v>
@@ -3835,13 +3835,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>552004</v>
+        <v>551916</v>
       </c>
       <c r="R31" t="n">
-        <v>7037805</v>
+        <v>7037885</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3895,44 +3895,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133026237</v>
+        <v>133026664</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>92290</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,13 +3942,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>551916</v>
+        <v>551892</v>
       </c>
       <c r="R32" t="n">
-        <v>7037885</v>
+        <v>7037942</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4002,12 +4002,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133028530</v>
+        <v>133015718</v>
       </c>
       <c r="B41" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,42 +4891,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>551656</v>
+        <v>551979</v>
       </c>
       <c r="R41" t="n">
-        <v>7038025</v>
+        <v>7037745</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4955,7 +4950,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4965,7 +4960,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4980,22 +4975,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133025002</v>
+        <v>133027021</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5003,37 +4998,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>552071</v>
+        <v>551803</v>
       </c>
       <c r="R42" t="n">
-        <v>7037735</v>
+        <v>7037914</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5072,7 +5072,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5087,22 +5092,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133015718</v>
+        <v>133022367</v>
       </c>
       <c r="B43" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5110,34 +5115,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>551979</v>
+        <v>552043</v>
       </c>
       <c r="R43" t="n">
-        <v>7037745</v>
+        <v>7037622</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5169,7 +5179,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5179,7 +5189,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5206,10 +5221,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133027021</v>
+        <v>133028530</v>
       </c>
       <c r="B44" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5217,16 +5232,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5237,7 +5252,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5246,13 +5261,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>551803</v>
+        <v>551656</v>
       </c>
       <c r="R44" t="n">
-        <v>7037914</v>
+        <v>7038025</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5281,7 +5296,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5291,12 +5306,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5311,22 +5321,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133022367</v>
+        <v>133025002</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5334,42 +5344,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>552043</v>
+        <v>552071</v>
       </c>
       <c r="R45" t="n">
-        <v>7037622</v>
+        <v>7037735</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5398,7 +5403,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5408,12 +5413,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5428,22 +5428,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133027884</v>
+        <v>133025648</v>
       </c>
       <c r="B46" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5451,43 +5451,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>551721</v>
+        <v>551981</v>
       </c>
       <c r="R46" t="n">
-        <v>7037978</v>
+        <v>7037784</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5519,7 +5510,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5529,7 +5520,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5556,10 +5547,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133025648</v>
+        <v>133027884</v>
       </c>
       <c r="B47" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5567,34 +5558,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>551981</v>
+        <v>551721</v>
       </c>
       <c r="R47" t="n">
-        <v>7037784</v>
+        <v>7037978</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6101,10 +6101,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133017895</v>
+        <v>133021235</v>
       </c>
       <c r="B52" t="n">
-        <v>56522</v>
+        <v>57958</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6112,27 +6112,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>552040</v>
+        <v>552097</v>
       </c>
       <c r="R52" t="n">
-        <v>7037573</v>
+        <v>7037521</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6186,7 +6186,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6213,7 +6218,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133021235</v>
+        <v>133019141</v>
       </c>
       <c r="B53" t="n">
         <v>57958</v>
@@ -6253,13 +6258,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>552097</v>
+        <v>552062</v>
       </c>
       <c r="R53" t="n">
-        <v>7037521</v>
+        <v>7037501</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6288,7 +6293,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6298,7 +6303,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6318,19 +6323,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133019141</v>
+        <v>133018677</v>
       </c>
       <c r="B54" t="n">
         <v>57958</v>
@@ -6370,13 +6375,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>552062</v>
+        <v>552058</v>
       </c>
       <c r="R54" t="n">
-        <v>7037501</v>
+        <v>7037536</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6405,7 +6410,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6415,7 +6420,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6435,22 +6440,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133018677</v>
+        <v>133017895</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>56522</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6458,27 +6463,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6487,10 +6492,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>552058</v>
+        <v>552040</v>
       </c>
       <c r="R55" t="n">
-        <v>7037536</v>
+        <v>7037573</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6522,7 +6527,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6532,12 +6537,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6793,10 +6793,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133016246</v>
+        <v>133023893</v>
       </c>
       <c r="B58" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6804,37 +6804,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>552069</v>
+        <v>552119</v>
       </c>
       <c r="R58" t="n">
-        <v>7037664</v>
+        <v>7037634</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6863,7 +6868,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6873,7 +6878,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6888,22 +6893,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133023893</v>
+        <v>133024844</v>
       </c>
       <c r="B59" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6911,16 +6916,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6931,7 +6936,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6940,13 +6945,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>552119</v>
+        <v>552094</v>
       </c>
       <c r="R59" t="n">
-        <v>7037634</v>
+        <v>7037684</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6975,7 +6980,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6985,7 +6990,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7000,22 +7005,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133028686</v>
+        <v>133016246</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7023,42 +7028,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>551645</v>
+        <v>552069</v>
       </c>
       <c r="R60" t="n">
-        <v>7038009</v>
+        <v>7037664</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7097,12 +7097,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7117,19 +7112,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133017265</v>
+        <v>133028686</v>
       </c>
       <c r="B61" t="n">
         <v>57958</v>
@@ -7169,13 +7164,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>551991</v>
+        <v>551645</v>
       </c>
       <c r="R61" t="n">
-        <v>7037644</v>
+        <v>7038009</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7204,7 +7199,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7214,7 +7209,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7234,22 +7229,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133024844</v>
+        <v>133017265</v>
       </c>
       <c r="B62" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7257,16 +7252,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7286,10 +7281,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>552094</v>
+        <v>551991</v>
       </c>
       <c r="R62" t="n">
-        <v>7037684</v>
+        <v>7037644</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7321,7 +7316,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7331,7 +7326,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133025403</v>
+        <v>133025666</v>
       </c>
       <c r="B65" t="n">
-        <v>79333</v>
+        <v>91914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7583,21 +7583,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>552034</v>
+        <v>551986</v>
       </c>
       <c r="R65" t="n">
-        <v>7037787</v>
+        <v>7037773</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7679,7 +7679,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133016328</v>
+        <v>133025403</v>
       </c>
       <c r="B66" t="n">
         <v>79333</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>552042</v>
+        <v>552034</v>
       </c>
       <c r="R66" t="n">
-        <v>7037659</v>
+        <v>7037787</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7786,10 +7786,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133025666</v>
+        <v>133016328</v>
       </c>
       <c r="B67" t="n">
-        <v>91914</v>
+        <v>79333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7797,21 +7797,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>551986</v>
+        <v>552042</v>
       </c>
       <c r="R67" t="n">
-        <v>7037773</v>
+        <v>7037659</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9354,10 +9354,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133024612</v>
+        <v>133025358</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9365,37 +9365,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>552097</v>
+        <v>552052</v>
       </c>
       <c r="R81" t="n">
-        <v>7037685</v>
+        <v>7037780</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9424,7 +9429,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9434,7 +9439,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9449,19 +9459,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133025358</v>
+        <v>133026519</v>
       </c>
       <c r="B82" t="n">
         <v>57958</v>
@@ -9501,10 +9511,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>552052</v>
+        <v>551914</v>
       </c>
       <c r="R82" t="n">
-        <v>7037780</v>
+        <v>7037935</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -9536,7 +9546,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9546,12 +9556,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på gran, färska och äldre spår</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9578,7 +9588,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133026519</v>
+        <v>133017996</v>
       </c>
       <c r="B83" t="n">
         <v>57958</v>
@@ -9614,14 +9624,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>551914</v>
+        <v>552026</v>
       </c>
       <c r="R83" t="n">
-        <v>7037935</v>
+        <v>7037570</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9653,7 +9663,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9663,12 +9673,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack på gran, färska och äldre spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9695,7 +9705,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133017996</v>
+        <v>133015812</v>
       </c>
       <c r="B84" t="n">
         <v>57958</v>
@@ -9731,17 +9741,17 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>552026</v>
+        <v>551983</v>
       </c>
       <c r="R84" t="n">
-        <v>7037570</v>
+        <v>7037744</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9770,7 +9780,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9780,12 +9790,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9800,19 +9810,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133015812</v>
+        <v>133025266</v>
       </c>
       <c r="B85" t="n">
         <v>57958</v>
@@ -9843,7 +9853,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9852,13 +9862,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>551983</v>
+        <v>552072</v>
       </c>
       <c r="R85" t="n">
-        <v>7037744</v>
+        <v>7037774</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9887,7 +9897,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9897,7 +9907,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9917,22 +9927,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133025266</v>
+        <v>133024612</v>
       </c>
       <c r="B86" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9940,42 +9950,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>552072</v>
+        <v>552097</v>
       </c>
       <c r="R86" t="n">
-        <v>7037774</v>
+        <v>7037685</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10004,7 +10009,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10014,12 +10019,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10034,22 +10034,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133020053</v>
+        <v>133025970</v>
       </c>
       <c r="B87" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10057,39 +10057,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>552014</v>
+        <v>551977</v>
       </c>
       <c r="R87" t="n">
-        <v>7037498</v>
+        <v>7037841</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10121,7 +10116,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10131,7 +10126,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10158,32 +10153,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133025970</v>
+        <v>133025202</v>
       </c>
       <c r="B88" t="n">
-        <v>79333</v>
+        <v>97243</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10193,13 +10188,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>551977</v>
+        <v>552070</v>
       </c>
       <c r="R88" t="n">
-        <v>7037841</v>
+        <v>7037765</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10228,7 +10223,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10238,7 +10233,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10253,57 +10248,62 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133025202</v>
+        <v>133017601</v>
       </c>
       <c r="B89" t="n">
-        <v>97243</v>
+        <v>57958</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>552070</v>
+        <v>551987</v>
       </c>
       <c r="R89" t="n">
-        <v>7037765</v>
+        <v>7037612</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10345,7 +10345,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10372,7 +10377,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133017601</v>
+        <v>133024456</v>
       </c>
       <c r="B90" t="n">
         <v>57958</v>
@@ -10403,22 +10408,22 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>551987</v>
+        <v>552118</v>
       </c>
       <c r="R90" t="n">
-        <v>7037612</v>
+        <v>7037678</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10447,7 +10452,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10457,7 +10462,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10477,19 +10482,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133024456</v>
+        <v>133027862</v>
       </c>
       <c r="B91" t="n">
         <v>57958</v>
@@ -10520,7 +10525,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10529,10 +10534,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>552118</v>
+        <v>551707</v>
       </c>
       <c r="R91" t="n">
-        <v>7037678</v>
+        <v>7038024</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10564,7 +10569,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10574,12 +10579,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10606,10 +10611,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133027862</v>
+        <v>133020053</v>
       </c>
       <c r="B92" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10617,16 +10622,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10642,14 +10647,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>551707</v>
+        <v>552014</v>
       </c>
       <c r="R92" t="n">
-        <v>7038024</v>
+        <v>7037498</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10681,7 +10686,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10691,12 +10696,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:12</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10723,10 +10723,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133016153</v>
+        <v>133017323</v>
       </c>
       <c r="B93" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10734,16 +10734,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>552049</v>
+        <v>551983</v>
       </c>
       <c r="R93" t="n">
-        <v>7037701</v>
+        <v>7037658</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10808,7 +10808,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack, Färska och äldre spår på gran</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10835,10 +10840,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133027652</v>
+        <v>133022907</v>
       </c>
       <c r="B94" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10846,37 +10851,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>551711</v>
+        <v>552082</v>
       </c>
       <c r="R94" t="n">
-        <v>7037996</v>
+        <v>7037634</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10905,7 +10915,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10915,7 +10925,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10930,60 +10945,65 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133021299</v>
+        <v>133027059</v>
       </c>
       <c r="B95" t="n">
-        <v>97243</v>
+        <v>57958</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>552094</v>
+        <v>551807</v>
       </c>
       <c r="R95" t="n">
-        <v>7037523</v>
+        <v>7037987</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11012,7 +11032,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11022,7 +11042,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11037,22 +11062,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133017323</v>
+        <v>133016153</v>
       </c>
       <c r="B96" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11060,16 +11085,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -11089,10 +11114,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>551983</v>
+        <v>552049</v>
       </c>
       <c r="R96" t="n">
-        <v>7037658</v>
+        <v>7037701</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -11124,7 +11149,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11134,12 +11159,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack, Färska och äldre spår på gran</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,10 +11186,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133022907</v>
+        <v>133027652</v>
       </c>
       <c r="B97" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11177,42 +11197,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>552082</v>
+        <v>551711</v>
       </c>
       <c r="R97" t="n">
-        <v>7037634</v>
+        <v>7037996</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11241,7 +11256,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11251,12 +11266,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11271,65 +11281,60 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133027059</v>
+        <v>133021299</v>
       </c>
       <c r="B98" t="n">
-        <v>57958</v>
+        <v>97243</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>551807</v>
+        <v>552094</v>
       </c>
       <c r="R98" t="n">
-        <v>7037987</v>
+        <v>7037523</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11358,7 +11363,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11368,12 +11373,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11388,22 +11388,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133026365</v>
+        <v>133016047</v>
       </c>
       <c r="B99" t="n">
-        <v>57955</v>
+        <v>79333</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11411,42 +11411,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>551913</v>
+        <v>552035</v>
       </c>
       <c r="R99" t="n">
-        <v>7037904</v>
+        <v>7037709</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11475,7 +11470,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11485,7 +11480,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11500,22 +11495,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133016003</v>
+        <v>133026365</v>
       </c>
       <c r="B100" t="n">
-        <v>79333</v>
+        <v>57955</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11523,37 +11518,42 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>552021</v>
+        <v>551913</v>
       </c>
       <c r="R100" t="n">
-        <v>7037732</v>
+        <v>7037904</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11607,19 +11607,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133016047</v>
+        <v>133016003</v>
       </c>
       <c r="B101" t="n">
         <v>79333</v>
@@ -11654,10 +11654,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>552035</v>
+        <v>552021</v>
       </c>
       <c r="R101" t="n">
-        <v>7037709</v>
+        <v>7037732</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12047,10 +12047,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133027032</v>
+        <v>133023354</v>
       </c>
       <c r="B105" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12058,42 +12058,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>551806</v>
+        <v>552115</v>
       </c>
       <c r="R105" t="n">
-        <v>7037991</v>
+        <v>7037637</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12122,7 +12117,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12132,7 +12127,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12147,22 +12142,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133016445</v>
+        <v>133024875</v>
       </c>
       <c r="B106" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12170,39 +12165,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>552020</v>
+        <v>552088</v>
       </c>
       <c r="R106" t="n">
-        <v>7037641</v>
+        <v>7037696</v>
       </c>
       <c r="S106" t="n">
         <v>20</v>
@@ -12234,7 +12224,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12244,12 +12234,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12276,10 +12261,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133023664</v>
+        <v>133027032</v>
       </c>
       <c r="B107" t="n">
-        <v>57958</v>
+        <v>57136</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12287,16 +12272,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12307,7 +12292,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12316,13 +12301,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>552114</v>
+        <v>551806</v>
       </c>
       <c r="R107" t="n">
-        <v>7037653</v>
+        <v>7037991</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12351,7 +12336,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12361,12 +12346,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:33</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12381,12 +12361,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12500,10 +12480,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133023354</v>
+        <v>133025768</v>
       </c>
       <c r="B109" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12511,21 +12491,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12535,13 +12515,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>552115</v>
+        <v>551962</v>
       </c>
       <c r="R109" t="n">
-        <v>7037637</v>
+        <v>7037809</v>
       </c>
       <c r="S109" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12570,7 +12550,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12580,7 +12560,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12595,22 +12575,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133025768</v>
+        <v>133016445</v>
       </c>
       <c r="B110" t="n">
-        <v>83181</v>
+        <v>57958</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12618,37 +12598,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>551962</v>
+        <v>552020</v>
       </c>
       <c r="R110" t="n">
-        <v>7037809</v>
+        <v>7037641</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12677,7 +12662,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12687,7 +12672,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12702,22 +12692,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133024875</v>
+        <v>133023664</v>
       </c>
       <c r="B111" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12725,34 +12715,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>552088</v>
+        <v>552114</v>
       </c>
       <c r="R111" t="n">
-        <v>7037696</v>
+        <v>7037653</v>
       </c>
       <c r="S111" t="n">
         <v>20</v>
@@ -12784,7 +12779,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12794,7 +12789,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13365,10 +13365,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133018000</v>
+        <v>133027635</v>
       </c>
       <c r="B117" t="n">
-        <v>79333</v>
+        <v>91914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13376,34 +13376,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
+          <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>552020</v>
+        <v>551706</v>
       </c>
       <c r="R117" t="n">
-        <v>7037558</v>
+        <v>7038000</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13472,10 +13472,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133027635</v>
+        <v>133028459</v>
       </c>
       <c r="B118" t="n">
-        <v>91914</v>
+        <v>57958</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13483,34 +13483,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>551706</v>
+        <v>551661</v>
       </c>
       <c r="R118" t="n">
-        <v>7038000</v>
+        <v>7038023</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13542,7 +13547,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13552,7 +13557,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13579,7 +13589,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133026771</v>
+        <v>133018000</v>
       </c>
       <c r="B119" t="n">
         <v>79333</v>
@@ -13610,14 +13620,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Isbillån, Isbillån, Ång</t>
+          <t>Nörd-Isbillkullen, Nörd-Isbillkullen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>551871</v>
+        <v>552020</v>
       </c>
       <c r="R119" t="n">
-        <v>7037938</v>
+        <v>7037558</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13649,7 +13659,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13659,7 +13669,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13686,10 +13696,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133028459</v>
+        <v>133026771</v>
       </c>
       <c r="B120" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13697,39 +13707,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Isbillån, Isbillån, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>551661</v>
+        <v>551871</v>
       </c>
       <c r="R120" t="n">
-        <v>7038023</v>
+        <v>7037938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13761,7 +13766,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13771,12 +13776,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD120" t="b">
